--- a/portfolio_data_extended.xlsx
+++ b/portfolio_data_extended.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Science Projects\portfolio_sql_data_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AE4769-F267-4E6A-B083-E7BE8E070318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC061A9-58B5-4FD2-A1C6-2401B746F875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17895" yWindow="4800" windowWidth="20565" windowHeight="12285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="securities" sheetId="1" r:id="rId1"/>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
